--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\catalogo_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06CD26BE-8DF7-4808-93F5-7420EE1B91BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B06F4C8-CB0D-41B9-94BB-908785170714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{02E3CDAF-A272-443C-8687-B38AE8A4CCA2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="77">
   <si>
     <t>Descrição</t>
   </si>
@@ -51,9 +51,6 @@
     <t>BIC 26 AL VIKING DIRT J.TUFF X-25 AZUL ESCURO/ AMARELO</t>
   </si>
   <si>
-    <t>BICICLETA 26</t>
-  </si>
-  <si>
     <t>83.0446</t>
   </si>
   <si>
@@ -153,9 +150,6 @@
     <t>83.0872</t>
   </si>
   <si>
-    <t>BICICLETA 29</t>
-  </si>
-  <si>
     <t>83.0883</t>
   </si>
   <si>
@@ -247,13 +241,31 @@
   </si>
   <si>
     <t>BICICLETA ARO 29 21V FIRST SMITT TAM 19 PRETO F/TIFFANY</t>
+  </si>
+  <si>
+    <t>83.0943</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 24V K7 FIRST LIFTY TAM 17.5 AZUL GALAXY/BRANCO - 54778</t>
+  </si>
+  <si>
+    <t>83.0944</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 24V K7 FIRST LIFTY TAM 17.5 FOSCO GRAFITE/ PRATA - 46904</t>
+  </si>
+  <si>
+    <t>BICICLETAS 26</t>
+  </si>
+  <si>
+    <t>BICICLETAS 29</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,12 +275,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -319,13 +325,13 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -640,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B5E345-C4B2-49FA-A914-04EE787905E0}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -671,566 +677,460 @@
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
       <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
       <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
       <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
       <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
       <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
       <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
       <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E10" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
       <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
       <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
       <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
       <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
       <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E15" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
       <c r="C16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
       <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" t="s">
-        <v>39</v>
-      </c>
       <c r="C18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1145.5</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1064.26</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E19" s="2">
-        <v>692.67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" t="s">
-        <v>45</v>
-      </c>
       <c r="C20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E20" s="2">
-        <v>692.67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E21" s="2">
-        <v>692.67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E22" s="2">
-        <v>692.67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E23" s="2">
-        <v>692.67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" t="s">
-        <v>53</v>
+        <v>48</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E24" s="2">
-        <v>692.67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E25" s="2">
-        <v>692.67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" t="s">
-        <v>60</v>
+        <v>52</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E26" s="2">
-        <v>692.67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E27" s="2">
-        <v>692.67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" t="s">
-        <v>64</v>
+        <v>59</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E28" s="2">
-        <v>692.67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B29" t="s">
-        <v>66</v>
+        <v>61</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E29" s="2">
-        <v>692.67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C30" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E30" s="2">
-        <v>692.67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="C31" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E31" s="2">
-        <v>692.67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>70</v>
+        <v>54</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C32" t="s">
-        <v>41</v>
-      </c>
-      <c r="D32" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E32" s="2">
-        <v>692.67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>71</v>
+        <v>55</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E33" s="2">
-        <v>692.67</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C34" t="s">
-        <v>41</v>
-      </c>
-      <c r="D34" s="2">
-        <v>733.64</v>
-      </c>
-      <c r="E34" s="2">
-        <v>692.67</v>
-      </c>
+      <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{32B5E345-C4B2-49FA-A914-04EE787905E0}"/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\catalogo_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B06F4C8-CB0D-41B9-94BB-908785170714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B0692C-DC5C-41A0-89F8-687478DBA645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{02E3CDAF-A272-443C-8687-B38AE8A4CCA2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="102">
   <si>
     <t>Descrição</t>
   </si>
@@ -93,12 +93,6 @@
     <t>BIC 26 AL VIKING DIRT J.TUFF X-25 ROSA/AZUL</t>
   </si>
   <si>
-    <t>83.0416</t>
-  </si>
-  <si>
-    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 ROSA/VERDE</t>
-  </si>
-  <si>
     <t>83.0425</t>
   </si>
   <si>
@@ -126,9 +120,6 @@
     <t>83.0829</t>
   </si>
   <si>
-    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 VERMELHO/ AZUL</t>
-  </si>
-  <si>
     <t>83.0452</t>
   </si>
   <si>
@@ -147,21 +138,9 @@
     <t>BIC 26 AL VIKING DIRT J.TUFF X-30 VERDE NEON</t>
   </si>
   <si>
-    <t>83.0872</t>
-  </si>
-  <si>
     <t>83.0883</t>
   </si>
   <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 15.5 FEM AMARELO NEON/ CUMBO - 50752</t>
-  </si>
-  <si>
-    <t>83.0884</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 15.5 FEM PRETO/AMARELO/LARANJA - 50756</t>
-  </si>
-  <si>
     <t>83.0867</t>
   </si>
   <si>
@@ -174,27 +153,12 @@
     <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 BEGE/ VERMELHO - 54782</t>
   </si>
   <si>
-    <t>83.0876</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 CINZA/ VERDE E ROXO - 54822</t>
-  </si>
-  <si>
     <t>83.0801</t>
   </si>
   <si>
     <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 PRETO/AMARELO/LARANJA - 48755</t>
   </si>
   <si>
-    <t>83.0889</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 VERDE CHICLETE/ AMARELO - 55027</t>
-  </si>
-  <si>
-    <t>83.0114</t>
-  </si>
-  <si>
     <t>83.0500</t>
   </si>
   <si>
@@ -207,42 +171,18 @@
     <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 19 LARANJA CHICLETE/CHUMBO - 52331</t>
   </si>
   <si>
-    <t>83.0818</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 19 PRATA/CHUMBO - 47026</t>
-  </si>
-  <si>
     <t>83.0822</t>
   </si>
   <si>
     <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 19 PRATA/TIFFANY - 50595</t>
   </si>
   <si>
-    <t>83.0803</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 19 PRETO/AMARELO/LARANJA - 48753</t>
-  </si>
-  <si>
     <t>83.0824</t>
   </si>
   <si>
     <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 21 FOSCO VERMELHO/CHUMBO - 47805</t>
   </si>
   <si>
-    <t xml:space="preserve">BICICLETA ARO 29 21V FIRST SMITT TAM 15,5 FEM VERMELHO F/PTO </t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST SMITT TAM 19 21V PTO/LILAS/PESSEGO</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST SMITT TAM 19 PRETO F/PTA</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST SMITT TAM 19 PRETO F/TIFFANY</t>
-  </si>
-  <si>
     <t>83.0943</t>
   </si>
   <si>
@@ -255,10 +195,145 @@
     <t>BICICLETA ARO 29 24V K7 FIRST LIFTY TAM 17.5 FOSCO GRAFITE/ PRATA - 46904</t>
   </si>
   <si>
-    <t>BICICLETAS 26</t>
-  </si>
-  <si>
-    <t>BICICLETAS 29</t>
+    <t>83.0905</t>
+  </si>
+  <si>
+    <t>BIC 29 TAM 15.5 21V FIRST GFT F/OURO SMITT KIT1</t>
+  </si>
+  <si>
+    <t>83.0915</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 15.5 FIRST FEM AMARELO EGG/ PRETO LIFTY - 54427</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 15.5 FIRST FEM AMARELO NEON/ CUMBO LIFTY - 50752</t>
+  </si>
+  <si>
+    <t>83.0922</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST BRANCO/ VERMELHO LIFTY - 55045</t>
+  </si>
+  <si>
+    <t>83.0942</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM LARANJA CHICLETE/ BRANCO LIFTY - 55433</t>
+  </si>
+  <si>
+    <t>83.0941</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO AZUL CAPRI/ CHUMBO LIFTY - 55591</t>
+  </si>
+  <si>
+    <t>83.0920</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO PRETO/ AZUL TIFFANY - 50619</t>
+  </si>
+  <si>
+    <t>83.0918</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO PRETO/ CHUMBO - 49415</t>
+  </si>
+  <si>
+    <t>83.0919</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO VERMELHO/ BRANCO E PRATA - 55374</t>
+  </si>
+  <si>
+    <t>83.0939</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO VERMELHO/ PRATA LIFTY - 55381</t>
+  </si>
+  <si>
+    <t>83.0940</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST GRAFITE/ CHUMBO LIFTY - 46030</t>
+  </si>
+  <si>
+    <t>83.0923</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST PRETO/ VERDE E AMARELO LIFTY - 46243</t>
+  </si>
+  <si>
+    <t>83.0925</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST VERMELHO/ PRATA - 55240</t>
+  </si>
+  <si>
+    <t>83.0814</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 FIRST BRANCO/ROSA - 48598</t>
+  </si>
+  <si>
+    <t>83.0897</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 FOSCO GRAFITE/ VERDE E ROXO - 54854</t>
+  </si>
+  <si>
+    <t>83.0890</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 FOSCO GRAFITE/ VERMELHO - 54838</t>
+  </si>
+  <si>
+    <t>83.0856</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 FOSCO VERMELHO/ CHUMBO - 46035</t>
+  </si>
+  <si>
+    <t>83.0901</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 GRAFITE/ VERDE E ROXO - 54806</t>
+  </si>
+  <si>
+    <t>83.0840</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 PRETO/PRATA - 46802</t>
+  </si>
+  <si>
+    <t>83.0817</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 19 AZUL HUNTER/PRATA - 47904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BICICLETA ARO 29 21V FIRST SMITT TAM 19 21V FIRST PRETO F/TIFFANY </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BICICLETA ARO 29 21V FIRST SMITT TAM 19 21V FIRST PTO/LILAS/PESSEGO </t>
+  </si>
+  <si>
+    <t>83.0927</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST FOSCO CINZA/ AZUL E ROXO LIFTY - 54845</t>
+  </si>
+  <si>
+    <t>83.0926</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST PRETO/ BRITO LIFTY - 48004</t>
+  </si>
+  <si>
+    <t>BICICLETA 26</t>
+  </si>
+  <si>
+    <t>BICICLETA 29</t>
   </si>
 </sst>
 </file>
@@ -322,14 +397,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -646,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B5E345-C4B2-49FA-A914-04EE787905E0}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -674,459 +745,600 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" t="s">
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" t="s">
         <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>30</v>
+      <c r="B14" t="s">
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>38</v>
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>41</v>
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" t="s">
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>43</v>
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>67</v>
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>45</v>
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>47</v>
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="s">
+        <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>49</v>
+      <c r="A24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>51</v>
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" t="s">
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>53</v>
+      <c r="A26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" t="s">
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>58</v>
+      <c r="A27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" t="s">
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>60</v>
+      <c r="A28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" t="s">
+        <v>75</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>62</v>
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>64</v>
+      <c r="A30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>68</v>
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s">
+        <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>69</v>
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>70</v>
+      <c r="A33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>66</v>
+      <c r="A34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>72</v>
+      <c r="A35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" t="s">
+        <v>85</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>74</v>
+      <c r="A36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" t="s">
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" t="s">
+        <v>101</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{32B5E345-C4B2-49FA-A914-04EE787905E0}"/>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\catalogo_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B0692C-DC5C-41A0-89F8-687478DBA645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518500FC-EECA-4052-B898-121369980FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{02E3CDAF-A272-443C-8687-B38AE8A4CCA2}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="130">
   <si>
     <t>Descrição</t>
   </si>
@@ -39,30 +39,12 @@
     <t>Categoria</t>
   </si>
   <si>
-    <t>Preço Antigo</t>
-  </si>
-  <si>
-    <t>Preço Promoção</t>
-  </si>
-  <si>
-    <t>83.0827</t>
-  </si>
-  <si>
-    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 AZUL ESCURO/ AMARELO</t>
-  </si>
-  <si>
     <t>83.0446</t>
   </si>
   <si>
     <t>BIC 26 AL VIKING DIRT J.TUFF X-25 AZUL/AMARELO</t>
   </si>
   <si>
-    <t>83.0413</t>
-  </si>
-  <si>
-    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 AZUL/LARANJA</t>
-  </si>
-  <si>
     <t>83.0704</t>
   </si>
   <si>
@@ -138,96 +120,36 @@
     <t>BIC 26 AL VIKING DIRT J.TUFF X-30 VERDE NEON</t>
   </si>
   <si>
-    <t>83.0883</t>
-  </si>
-  <si>
     <t>83.0867</t>
   </si>
   <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 BEGE/ AZUL E ROXO - 54766</t>
-  </si>
-  <si>
     <t>83.0875</t>
   </si>
   <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 BEGE/ VERMELHO - 54782</t>
-  </si>
-  <si>
-    <t>83.0801</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 PRETO/AMARELO/LARANJA - 48755</t>
-  </si>
-  <si>
     <t>83.0500</t>
   </si>
   <si>
     <t>83.0428</t>
   </si>
   <si>
-    <t>83.0891</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 19 LARANJA CHICLETE/CHUMBO - 52331</t>
-  </si>
-  <si>
-    <t>83.0822</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 19 PRATA/TIFFANY - 50595</t>
-  </si>
-  <si>
     <t>83.0824</t>
   </si>
   <si>
     <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 21 FOSCO VERMELHO/CHUMBO - 47805</t>
   </si>
   <si>
-    <t>83.0943</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 24V K7 FIRST LIFTY TAM 17.5 AZUL GALAXY/BRANCO - 54778</t>
-  </si>
-  <si>
     <t>83.0944</t>
   </si>
   <si>
     <t>BICICLETA ARO 29 24V K7 FIRST LIFTY TAM 17.5 FOSCO GRAFITE/ PRATA - 46904</t>
   </si>
   <si>
-    <t>83.0905</t>
-  </si>
-  <si>
-    <t>BIC 29 TAM 15.5 21V FIRST GFT F/OURO SMITT KIT1</t>
-  </si>
-  <si>
-    <t>83.0915</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 15.5 FIRST FEM AMARELO EGG/ PRETO LIFTY - 54427</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 15.5 FIRST FEM AMARELO NEON/ CUMBO LIFTY - 50752</t>
-  </si>
-  <si>
-    <t>83.0922</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST BRANCO/ VERMELHO LIFTY - 55045</t>
-  </si>
-  <si>
     <t>83.0942</t>
   </si>
   <si>
     <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM LARANJA CHICLETE/ BRANCO LIFTY - 55433</t>
   </si>
   <si>
-    <t>83.0941</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO AZUL CAPRI/ CHUMBO LIFTY - 55591</t>
-  </si>
-  <si>
     <t>83.0920</t>
   </si>
   <si>
@@ -273,57 +195,18 @@
     <t>83.0814</t>
   </si>
   <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 FIRST BRANCO/ROSA - 48598</t>
-  </si>
-  <si>
     <t>83.0897</t>
   </si>
   <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 FOSCO GRAFITE/ VERDE E ROXO - 54854</t>
-  </si>
-  <si>
-    <t>83.0890</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 FOSCO GRAFITE/ VERMELHO - 54838</t>
-  </si>
-  <si>
     <t>83.0856</t>
   </si>
   <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 FOSCO VERMELHO/ CHUMBO - 46035</t>
-  </si>
-  <si>
     <t>83.0901</t>
   </si>
   <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 GRAFITE/ VERDE E ROXO - 54806</t>
-  </si>
-  <si>
-    <t>83.0840</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 PRETO/PRATA - 46802</t>
-  </si>
-  <si>
     <t>83.0817</t>
   </si>
   <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 19 AZUL HUNTER/PRATA - 47904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BICICLETA ARO 29 21V FIRST SMITT TAM 19 21V FIRST PRETO F/TIFFANY </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BICICLETA ARO 29 21V FIRST SMITT TAM 19 21V FIRST PTO/LILAS/PESSEGO </t>
-  </si>
-  <si>
-    <t>83.0927</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 19 FIRST FOSCO CINZA/ AZUL E ROXO LIFTY - 54845</t>
-  </si>
-  <si>
     <t>83.0926</t>
   </si>
   <si>
@@ -334,26 +217,220 @@
   </si>
   <si>
     <t>BICICLETA 29</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 VERMELHO/ AZUL</t>
+  </si>
+  <si>
+    <t>83.0680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BICICLETA ARO 29 21V FIRST TAM 15,5 OURO/PTO SMITT </t>
+  </si>
+  <si>
+    <t>83.0846</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST TAM 15.5 AZUL GALAXY/ BRANCO LIFTY - 54779</t>
+  </si>
+  <si>
+    <t>83.0957</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST TAM 15.5 FIRST FEM BRANCO/ LARANJA E AMARELO LIFTY - 51743</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST BEGE/ AZUL E ROXO LIFTY - 54766</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST 17.5 BEGE/ VERMELHO LIFTY  - 54782</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST BRANCO/ROSA LIFTY - 48598</t>
+  </si>
+  <si>
+    <t>83.0877</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO GRAFITE/ PRATA LIFTY - 46904</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO GRAFITE/ VERDE E ROXO LIFTY - 54854</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO VERMELHO/ CHUMBO LIFTY - 46035</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST GRAFITE/ VERDE E ROXO LIFTY - 54806</t>
+  </si>
+  <si>
+    <t>83.0782</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST GRAFITE/VERDE/AMARELO LIFTY - 46659</t>
+  </si>
+  <si>
+    <t>83.0962</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM  17.5 FIRST CINZA/ CHUMBO LIFTY - 51208</t>
+  </si>
+  <si>
+    <t>83.0960</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST AZUL ZIMBRO/ CHUMBO LIFTY - 49214</t>
+  </si>
+  <si>
+    <t>83.0963</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST BRANCO/ ROXO LIFTY - 54798</t>
+  </si>
+  <si>
+    <t>83.0959</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST CINZA/ AZUL E ROXO LIFTY - 54826</t>
+  </si>
+  <si>
+    <t>83.0961</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM AZUL CAPRI/ PRATA LIFTY - 54565</t>
+  </si>
+  <si>
+    <t>83.0956</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM LILAS/ CHUMBO LIFTY - 55507</t>
+  </si>
+  <si>
+    <t>83.0958</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST VERDE MILITAR/ AZUL E ROXO LIFTY - 54758</t>
+  </si>
+  <si>
+    <t>83.0952</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST VERDE MILITAR/ CHUMBO LIFTY - 48552</t>
+  </si>
+  <si>
+    <t>BICIXLETA ARO 29 21V TAM 19 FIRST PRETO F/TIFFANY SMITT KIT1</t>
+  </si>
+  <si>
+    <t>BICIXLETA ARO 29 21V TAM 19 FIRST PTO/LILAS/PESSEGO SMITT KIT1</t>
+  </si>
+  <si>
+    <t>83.0841</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST AZUL GALAXY/VERMELHO LIFTY - 54773</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST  AZUL HUNTER/PRATA LIFTY - 47904</t>
+  </si>
+  <si>
+    <t>83.0795</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST BRANCO/BRITO LIFTY - 48447</t>
+  </si>
+  <si>
+    <t>83.0837</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST BRANCO/LARANJA/AMARELO LIFTY - 49318</t>
+  </si>
+  <si>
+    <t>83.0818</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST PRATA/CHUMBO LIFTY - 47026</t>
+  </si>
+  <si>
+    <t>83.0803</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST PRETO/AMARELO/LARANJA LIFTY - 48753</t>
+  </si>
+  <si>
+    <t>83.0892</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 21 AZUL GALAXY/ VERMELHO - 54772</t>
+  </si>
+  <si>
+    <t>83.0825</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM19 VERDE CHICLETE/CHUMBO - 52328</t>
+  </si>
+  <si>
+    <t>83.0965</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST AZUL HUNTER/ CHUMBO LIFTY - 49094</t>
+  </si>
+  <si>
+    <t>83.0964</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST FOSCO PRATA/ CHUMBO LIFTY - 47028</t>
+  </si>
+  <si>
+    <t>83.0930</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST FOSCO PRETO/VERDE/AMARELO LIFTY - 50621</t>
+  </si>
+  <si>
+    <t>83.0966</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST FOSCO VERDE MILITAR/ AZUL E ROXO LIFTY - 54833</t>
+  </si>
+  <si>
+    <t>83.0953</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST VERDE MILITAR/ PRATA LIFTY - 49464</t>
+  </si>
+  <si>
+    <t>83.0967</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST VERMELHO/ BRANCO E PRATA LIFTY - 55194</t>
+  </si>
+  <si>
+    <t>83.0934</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 21 FIRST VERDE MILITAR/ PRATA LIFTY - 49421</t>
+  </si>
+  <si>
+    <t>15.5</t>
+  </si>
+  <si>
+    <t>17.5</t>
+  </si>
+  <si>
+    <t>Tamanho da Bicicleta</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -370,7 +447,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -393,14 +470,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -717,17 +806,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B5E345-C4B2-49FA-A914-04EE787905E0}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="82.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -737,500 +825,515 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="C8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>20</v>
       </c>
-      <c r="C9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B13" t="s">
         <v>25</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="C12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>28</v>
       </c>
-      <c r="C13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B15" t="s">
         <v>29</v>
       </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="C15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>30</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>31</v>
       </c>
-      <c r="C15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>55</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>56</v>
       </c>
-      <c r="C18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>57</v>
       </c>
-      <c r="B19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>68</v>
-      </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
-      </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>38</v>
       </c>
-      <c r="C31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>39</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>40</v>
       </c>
-      <c r="C32" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>80</v>
-      </c>
-      <c r="B33" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>82</v>
-      </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
-      </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>92</v>
       </c>
@@ -1238,111 +1341,323 @@
         <v>93</v>
       </c>
       <c r="C40" t="s">
+        <v>62</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" t="s">
+        <v>62</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" t="s">
+        <v>62</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" t="s">
+        <v>62</v>
+      </c>
+      <c r="F43" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>33</v>
+      </c>
+      <c r="B44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" t="s">
+        <v>62</v>
+      </c>
+      <c r="F44" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" t="s">
+        <v>62</v>
+      </c>
+      <c r="F45" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" t="s">
+        <v>62</v>
+      </c>
+      <c r="F46" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>47</v>
-      </c>
-      <c r="B42" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>96</v>
-      </c>
-      <c r="B45" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>98</v>
-      </c>
-      <c r="B46" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>49</v>
-      </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F47" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="F48" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>62</v>
+      </c>
+      <c r="F49" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" t="s">
+        <v>62</v>
+      </c>
+      <c r="F50" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>109</v>
+      </c>
+      <c r="B51" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" t="s">
+        <v>62</v>
+      </c>
+      <c r="F51" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" t="s">
+        <v>35</v>
+      </c>
+      <c r="C52" t="s">
+        <v>62</v>
+      </c>
+      <c r="F52" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>111</v>
+      </c>
+      <c r="B53" t="s">
+        <v>112</v>
+      </c>
+      <c r="C53" t="s">
+        <v>62</v>
+      </c>
+      <c r="F53" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>113</v>
+      </c>
+      <c r="B54" t="s">
+        <v>114</v>
+      </c>
+      <c r="C54" t="s">
+        <v>62</v>
+      </c>
+      <c r="F54" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>115</v>
+      </c>
+      <c r="B55" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" t="s">
+        <v>62</v>
+      </c>
+      <c r="F55" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>117</v>
+      </c>
+      <c r="B56" t="s">
+        <v>118</v>
+      </c>
+      <c r="C56" t="s">
+        <v>62</v>
+      </c>
+      <c r="F56" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>119</v>
+      </c>
+      <c r="B57" t="s">
+        <v>120</v>
+      </c>
+      <c r="C57" t="s">
+        <v>62</v>
+      </c>
+      <c r="F57" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" t="s">
+        <v>62</v>
+      </c>
+      <c r="F58" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>121</v>
+      </c>
+      <c r="B59" t="s">
+        <v>122</v>
+      </c>
+      <c r="C59" t="s">
+        <v>62</v>
+      </c>
+      <c r="F59" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>123</v>
+      </c>
+      <c r="B60" t="s">
+        <v>124</v>
+      </c>
+      <c r="C60" t="s">
+        <v>62</v>
+      </c>
+      <c r="F60" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" t="s">
+        <v>126</v>
+      </c>
+      <c r="C61" t="s">
+        <v>62</v>
+      </c>
+      <c r="F61" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62" t="s">
+        <v>62</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{32B5E345-C4B2-49FA-A914-04EE787905E0}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <autoFilter ref="A1:C62" xr:uid="{32B5E345-C4B2-49FA-A914-04EE787905E0}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\catalogo_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518500FC-EECA-4052-B898-121369980FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A48C3E-E381-40B6-83ED-9AB7CAB8F832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{02E3CDAF-A272-443C-8687-B38AE8A4CCA2}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{02E3CDAF-A272-443C-8687-B38AE8A4CCA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="98">
   <si>
     <t>Descrição</t>
   </si>
@@ -39,12 +39,6 @@
     <t>Categoria</t>
   </si>
   <si>
-    <t>83.0446</t>
-  </si>
-  <si>
-    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 AZUL/AMARELO</t>
-  </si>
-  <si>
     <t>83.0704</t>
   </si>
   <si>
@@ -144,24 +138,6 @@
     <t>BICICLETA ARO 29 24V K7 FIRST LIFTY TAM 17.5 FOSCO GRAFITE/ PRATA - 46904</t>
   </si>
   <si>
-    <t>83.0942</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM LARANJA CHICLETE/ BRANCO LIFTY - 55433</t>
-  </si>
-  <si>
-    <t>83.0920</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO PRETO/ AZUL TIFFANY - 50619</t>
-  </si>
-  <si>
-    <t>83.0918</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO PRETO/ CHUMBO - 49415</t>
-  </si>
-  <si>
     <t>83.0919</t>
   </si>
   <si>
@@ -174,39 +150,12 @@
     <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO VERMELHO/ PRATA LIFTY - 55381</t>
   </si>
   <si>
-    <t>83.0940</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST GRAFITE/ CHUMBO LIFTY - 46030</t>
-  </si>
-  <si>
     <t>83.0923</t>
   </si>
   <si>
     <t>BICICLETA ARO 29 21V TAM 17.5 FIRST PRETO/ VERDE E AMARELO LIFTY - 46243</t>
   </si>
   <si>
-    <t>83.0925</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST VERMELHO/ PRATA - 55240</t>
-  </si>
-  <si>
-    <t>83.0814</t>
-  </si>
-  <si>
-    <t>83.0897</t>
-  </si>
-  <si>
-    <t>83.0856</t>
-  </si>
-  <si>
-    <t>83.0901</t>
-  </si>
-  <si>
-    <t>83.0817</t>
-  </si>
-  <si>
     <t>83.0926</t>
   </si>
   <si>
@@ -222,66 +171,6 @@
     <t>BIC 26 AL VIKING DIRT J.TUFF X-25 VERMELHO/ AZUL</t>
   </si>
   <si>
-    <t>83.0680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BICICLETA ARO 29 21V FIRST TAM 15,5 OURO/PTO SMITT </t>
-  </si>
-  <si>
-    <t>83.0846</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST TAM 15.5 AZUL GALAXY/ BRANCO LIFTY - 54779</t>
-  </si>
-  <si>
-    <t>83.0957</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST TAM 15.5 FIRST FEM BRANCO/ LARANJA E AMARELO LIFTY - 51743</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST BEGE/ AZUL E ROXO LIFTY - 54766</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST 17.5 BEGE/ VERMELHO LIFTY  - 54782</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST BRANCO/ROSA LIFTY - 48598</t>
-  </si>
-  <si>
-    <t>83.0877</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO GRAFITE/ PRATA LIFTY - 46904</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO GRAFITE/ VERDE E ROXO LIFTY - 54854</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO VERMELHO/ CHUMBO LIFTY - 46035</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST GRAFITE/ VERDE E ROXO LIFTY - 54806</t>
-  </si>
-  <si>
-    <t>83.0782</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST GRAFITE/VERDE/AMARELO LIFTY - 46659</t>
-  </si>
-  <si>
-    <t>83.0962</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM  17.5 FIRST CINZA/ CHUMBO LIFTY - 51208</t>
-  </si>
-  <si>
-    <t>83.0960</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST AZUL ZIMBRO/ CHUMBO LIFTY - 49214</t>
-  </si>
-  <si>
     <t>83.0963</t>
   </si>
   <si>
@@ -294,93 +183,21 @@
     <t>BICICLETA ARO 29 21V TAM 17.5 FIRST CINZA/ AZUL E ROXO LIFTY - 54826</t>
   </si>
   <si>
-    <t>83.0961</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM AZUL CAPRI/ PRATA LIFTY - 54565</t>
-  </si>
-  <si>
-    <t>83.0956</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM LILAS/ CHUMBO LIFTY - 55507</t>
-  </si>
-  <si>
-    <t>83.0958</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST VERDE MILITAR/ AZUL E ROXO LIFTY - 54758</t>
-  </si>
-  <si>
     <t>83.0952</t>
   </si>
   <si>
     <t>BICICLETA ARO 29 21V TAM 17.5 FIRST VERDE MILITAR/ CHUMBO LIFTY - 48552</t>
   </si>
   <si>
-    <t>BICIXLETA ARO 29 21V TAM 19 FIRST PRETO F/TIFFANY SMITT KIT1</t>
-  </si>
-  <si>
-    <t>BICIXLETA ARO 29 21V TAM 19 FIRST PTO/LILAS/PESSEGO SMITT KIT1</t>
-  </si>
-  <si>
-    <t>83.0841</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 19 FIRST AZUL GALAXY/VERMELHO LIFTY - 54773</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 19 FIRST  AZUL HUNTER/PRATA LIFTY - 47904</t>
-  </si>
-  <si>
     <t>83.0795</t>
   </si>
   <si>
-    <t>BICICLETA ARO 29 21V TAM 19 FIRST BRANCO/BRITO LIFTY - 48447</t>
-  </si>
-  <si>
-    <t>83.0837</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 19 FIRST BRANCO/LARANJA/AMARELO LIFTY - 49318</t>
-  </si>
-  <si>
-    <t>83.0818</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 19 FIRST PRATA/CHUMBO LIFTY - 47026</t>
-  </si>
-  <si>
-    <t>83.0803</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 19 FIRST PRETO/AMARELO/LARANJA LIFTY - 48753</t>
-  </si>
-  <si>
-    <t>83.0892</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 21 AZUL GALAXY/ VERMELHO - 54772</t>
-  </si>
-  <si>
     <t>83.0825</t>
   </si>
   <si>
     <t>BICICLETA ARO 29 21V FIRST LIFTY TAM19 VERDE CHICLETE/CHUMBO - 52328</t>
   </si>
   <si>
-    <t>83.0965</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 19 FIRST AZUL HUNTER/ CHUMBO LIFTY - 49094</t>
-  </si>
-  <si>
-    <t>83.0964</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 19 FIRST FOSCO PRATA/ CHUMBO LIFTY - 47028</t>
-  </si>
-  <si>
     <t>83.0930</t>
   </si>
   <si>
@@ -399,18 +216,6 @@
     <t>BICICLETA ARO 29 21V TAM 19 FIRST VERDE MILITAR/ PRATA LIFTY - 49464</t>
   </si>
   <si>
-    <t>83.0967</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 19 FIRST VERMELHO/ BRANCO E PRATA LIFTY - 55194</t>
-  </si>
-  <si>
-    <t>83.0934</t>
-  </si>
-  <si>
-    <t>BICICLETA ARO 29 21V TAM 21 FIRST VERDE MILITAR/ PRATA LIFTY - 49421</t>
-  </si>
-  <si>
     <t>15.5</t>
   </si>
   <si>
@@ -418,6 +223,105 @@
   </si>
   <si>
     <t>Tamanho da Bicicleta</t>
+  </si>
+  <si>
+    <t>83.0827</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 AZUL ESCURO/ AMARELO</t>
+  </si>
+  <si>
+    <t>83.0779</t>
+  </si>
+  <si>
+    <t>BIC 29 TAM 15.5 21V FIRST VERMELHO FOSCO/PRETO SMITT KIT1</t>
+  </si>
+  <si>
+    <t>83.0781</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 15.5 BRANCO/BRITO - 48445</t>
+  </si>
+  <si>
+    <t>83.0980</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 15.5 FIRST AZUL GALAXY/ PRATA LIFTY - 52321</t>
+  </si>
+  <si>
+    <t>83.0981</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 15.5 FIRST FEM GRAFITE/ PRATA LIFTY - 50561</t>
+  </si>
+  <si>
+    <t>83.0810</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 AZUL GALAXY/VERMELHO - 54774</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 BEGE/ AZUL E ROXO - 54766</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 17.5 BEGE/ VERMELHO - 54782</t>
+  </si>
+  <si>
+    <t>83.0977</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST AZUL CAPRI/ PRATA LIFTY -46907</t>
+  </si>
+  <si>
+    <t>83.0982</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST AZUL GALAXY/ CHUMBO LIFTY - 54142</t>
+  </si>
+  <si>
+    <t>83.0968</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM AMARELO NEON/ PRATA LIFTY - 54566</t>
+  </si>
+  <si>
+    <t>83.0979</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM FOSCO VIOLETA/ PRATA LIFTY - 55536</t>
+  </si>
+  <si>
+    <t>83.0975</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM LARANJA CHICLETE/ CHUMBO LIFTY - 54563</t>
+  </si>
+  <si>
+    <t>83.0976</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM VERMELHO/ BRANCO LIFTY - 55401</t>
+  </si>
+  <si>
+    <t>83.0978</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST LARANJA CHICLETE/ CHUMBO LIFTY - 52332</t>
+  </si>
+  <si>
+    <t>83.0983</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST VERDE MILITAR/ BRANCO LIFTY - 54761</t>
+  </si>
+  <si>
+    <t>BIC 29 TAM 19 21V FIRST PRETO F/TIFFANY SMITT KIT1</t>
+  </si>
+  <si>
+    <t>BIC 29 TAM 19 21V FIRST PTO/LILAS/PESSEGO SMITT KIT1</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 19 BRANCO/BRITO - 48447</t>
   </si>
 </sst>
 </file>
@@ -488,7 +392,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -806,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B5E345-C4B2-49FA-A914-04EE787905E0}">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -826,399 +730,385 @@
         <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>129</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" t="s">
         <v>62</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" t="s">
         <v>62</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" t="s">
         <v>62</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
         <v>62</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>128</v>
+        <v>76</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>128</v>
+        <v>77</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>128</v>
+        <v>78</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>128</v>
+        <v>80</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>128</v>
+        <v>82</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" t="s">
-        <v>62</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>128</v>
+        <v>48</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>128</v>
+        <v>50</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>128</v>
+        <v>84</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" t="s">
-        <v>62</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>128</v>
+        <v>86</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" t="s">
-        <v>62</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>128</v>
+        <v>88</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" t="s">
-        <v>62</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>128</v>
+        <v>90</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" t="s">
-        <v>62</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>128</v>
+        <v>37</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1228,25 +1118,25 @@
       <c r="B32" t="s">
         <v>39</v>
       </c>
-      <c r="C32" t="s">
-        <v>62</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>128</v>
+      <c r="C32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" t="s">
-        <v>62</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>128</v>
+        <v>92</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F33" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1256,407 +1146,183 @@
       <c r="B34" t="s">
         <v>41</v>
       </c>
-      <c r="C34" t="s">
-        <v>62</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>128</v>
+      <c r="C34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" t="s">
-        <v>62</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>128</v>
+        <v>52</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" t="s">
-        <v>62</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>128</v>
+        <v>57</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36">
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" t="s">
-        <v>62</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>128</v>
+        <v>59</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F37">
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" t="s">
-        <v>62</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>128</v>
+        <v>43</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38">
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" t="s">
-        <v>62</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>128</v>
+        <v>94</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F39">
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>128</v>
+        <v>61</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F40">
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="B41" t="s">
         <v>95</v>
       </c>
-      <c r="C41" t="s">
-        <v>62</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>128</v>
+      <c r="C41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41">
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" t="s">
-        <v>62</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>128</v>
+        <v>96</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42">
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
-      </c>
-      <c r="C43" t="s">
-        <v>62</v>
-      </c>
-      <c r="F43" s="3">
+        <v>97</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F43">
         <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" t="s">
-        <v>62</v>
-      </c>
-      <c r="F44" s="3">
+        <v>55</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44">
         <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
-      </c>
-      <c r="C45" t="s">
-        <v>62</v>
-      </c>
-      <c r="F45" s="3">
-        <v>19</v>
+        <v>33</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45">
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
-      </c>
-      <c r="C46" t="s">
-        <v>62</v>
-      </c>
-      <c r="F46" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>101</v>
-      </c>
-      <c r="B47" t="s">
-        <v>102</v>
-      </c>
-      <c r="C47" t="s">
-        <v>62</v>
-      </c>
-      <c r="F47" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>103</v>
-      </c>
-      <c r="B48" t="s">
-        <v>104</v>
-      </c>
-      <c r="C48" t="s">
-        <v>62</v>
-      </c>
-      <c r="F48" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>105</v>
-      </c>
-      <c r="B49" t="s">
-        <v>106</v>
-      </c>
-      <c r="C49" t="s">
-        <v>62</v>
-      </c>
-      <c r="F49" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>107</v>
-      </c>
-      <c r="B50" t="s">
-        <v>108</v>
-      </c>
-      <c r="C50" t="s">
-        <v>62</v>
-      </c>
-      <c r="F50" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>109</v>
-      </c>
-      <c r="B51" t="s">
-        <v>110</v>
-      </c>
-      <c r="C51" t="s">
-        <v>62</v>
-      </c>
-      <c r="F51" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>34</v>
-      </c>
-      <c r="B52" t="s">
         <v>35</v>
       </c>
-      <c r="C52" t="s">
-        <v>62</v>
-      </c>
-      <c r="F52" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>111</v>
-      </c>
-      <c r="B53" t="s">
-        <v>112</v>
-      </c>
-      <c r="C53" t="s">
-        <v>62</v>
-      </c>
-      <c r="F53" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>113</v>
-      </c>
-      <c r="B54" t="s">
-        <v>114</v>
-      </c>
-      <c r="C54" t="s">
-        <v>62</v>
-      </c>
-      <c r="F54" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>115</v>
-      </c>
-      <c r="B55" t="s">
-        <v>116</v>
-      </c>
-      <c r="C55" t="s">
-        <v>62</v>
-      </c>
-      <c r="F55" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>117</v>
-      </c>
-      <c r="B56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C56" t="s">
-        <v>62</v>
-      </c>
-      <c r="F56" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>119</v>
-      </c>
-      <c r="B57" t="s">
-        <v>120</v>
-      </c>
-      <c r="C57" t="s">
-        <v>62</v>
-      </c>
-      <c r="F57" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58" t="s">
-        <v>62</v>
-      </c>
-      <c r="F58" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>121</v>
-      </c>
-      <c r="B59" t="s">
-        <v>122</v>
-      </c>
-      <c r="C59" t="s">
-        <v>62</v>
-      </c>
-      <c r="F59" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>123</v>
-      </c>
-      <c r="B60" t="s">
-        <v>124</v>
-      </c>
-      <c r="C60" t="s">
-        <v>62</v>
-      </c>
-      <c r="F60" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>125</v>
-      </c>
-      <c r="B61" t="s">
-        <v>126</v>
-      </c>
-      <c r="C61" t="s">
-        <v>62</v>
-      </c>
-      <c r="F61" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>36</v>
-      </c>
-      <c r="B62" t="s">
-        <v>37</v>
-      </c>
-      <c r="C62" t="s">
-        <v>62</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>128</v>
+      <c r="C46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F46" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C62" xr:uid="{32B5E345-C4B2-49FA-A914-04EE787905E0}"/>
+  <autoFilter ref="A1:C46" xr:uid="{32B5E345-C4B2-49FA-A914-04EE787905E0}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\catalogo_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D75DC4A-3826-4E22-803B-1E6B3C1289C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F13E6B7-CB2B-4453-A3D6-11E87E52FAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{02E3CDAF-A272-443C-8687-B38AE8A4CCA2}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{02E3CDAF-A272-443C-8687-B38AE8A4CCA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="102">
   <si>
     <t>Descrição</t>
   </si>
@@ -322,13 +322,25 @@
   </si>
   <si>
     <t>19 24V</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>DESCRIÇÃO BICICLETA 26 VIKING</t>
+  </si>
+  <si>
+    <t>DESCRIÇÃO BICICLETA 29 FIRST 21V</t>
+  </si>
+  <si>
+    <t>DESCRIÇÃO BICICLETA 29 FIRST 24V</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -341,6 +353,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -389,10 +407,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -707,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B5E345-C4B2-49FA-A914-04EE787905E0}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -716,7 +737,7 @@
     <col min="6" max="6" width="21.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -729,8 +750,11 @@
       <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -740,8 +764,11 @@
       <c r="C2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -751,8 +778,11 @@
       <c r="C3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -762,8 +792,11 @@
       <c r="C4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -773,8 +806,11 @@
       <c r="C5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -784,8 +820,11 @@
       <c r="C6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>37</v>
       </c>
@@ -795,8 +834,11 @@
       <c r="C7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -806,8 +848,11 @@
       <c r="C8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -817,8 +862,11 @@
       <c r="C9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>48</v>
       </c>
@@ -831,8 +879,11 @@
       <c r="F10" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
@@ -845,8 +896,11 @@
       <c r="F11" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -859,8 +913,11 @@
       <c r="F12" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>73</v>
       </c>
@@ -873,8 +930,11 @@
       <c r="F13" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
@@ -887,8 +947,11 @@
       <c r="F14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>75</v>
       </c>
@@ -901,8 +964,11 @@
       <c r="F15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>77</v>
       </c>
@@ -915,8 +981,11 @@
       <c r="F16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -929,8 +998,11 @@
       <c r="F17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>52</v>
       </c>
@@ -943,8 +1015,11 @@
       <c r="F18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>53</v>
       </c>
@@ -957,8 +1032,11 @@
       <c r="F19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
@@ -971,8 +1049,11 @@
       <c r="F20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>54</v>
       </c>
@@ -985,8 +1066,11 @@
       <c r="F21" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>79</v>
       </c>
@@ -999,8 +1083,11 @@
       <c r="F22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
@@ -1013,8 +1100,11 @@
       <c r="F23" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G23" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -1027,8 +1117,11 @@
       <c r="F24" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>81</v>
       </c>
@@ -1041,8 +1134,11 @@
       <c r="F25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>83</v>
       </c>
@@ -1055,8 +1151,11 @@
       <c r="F26" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -1069,8 +1168,11 @@
       <c r="F27" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G27" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>85</v>
       </c>
@@ -1083,8 +1185,11 @@
       <c r="F28" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G28" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>65</v>
       </c>
@@ -1097,8 +1202,11 @@
       <c r="F29" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>87</v>
       </c>
@@ -1111,8 +1219,11 @@
       <c r="F30">
         <v>19</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G30" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>67</v>
       </c>
@@ -1125,8 +1236,11 @@
       <c r="F31">
         <v>19</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G31" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>69</v>
       </c>
@@ -1139,8 +1253,11 @@
       <c r="F32">
         <v>19</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G32" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>58</v>
       </c>
@@ -1153,8 +1270,11 @@
       <c r="F33">
         <v>19</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G33" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>59</v>
       </c>
@@ -1167,8 +1287,11 @@
       <c r="F34">
         <v>19</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G34" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>71</v>
       </c>
@@ -1181,8 +1304,11 @@
       <c r="F35">
         <v>19</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G35" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>89</v>
       </c>
@@ -1195,8 +1321,11 @@
       <c r="F36">
         <v>19</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>44</v>
       </c>
@@ -1209,8 +1338,11 @@
       <c r="F37">
         <v>19</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G37" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
@@ -1223,8 +1355,11 @@
       <c r="F38">
         <v>19</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G38" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -1237,8 +1372,11 @@
       <c r="F39">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>60</v>
       </c>
@@ -1251,8 +1389,11 @@
       <c r="F40">
         <v>19</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G40" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>91</v>
       </c>
@@ -1265,8 +1406,11 @@
       <c r="F41">
         <v>21</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G41" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>93</v>
       </c>
@@ -1279,8 +1423,11 @@
       <c r="F42">
         <v>21</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G42" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>95</v>
       </c>
@@ -1293,8 +1440,11 @@
       <c r="F43" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G43" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>27</v>
       </c>
@@ -1307,8 +1457,11 @@
       <c r="F44" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G44" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>11</v>
       </c>
@@ -1320,6 +1473,9 @@
       </c>
       <c r="F45" t="s">
         <v>64</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\catalogo_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F13E6B7-CB2B-4453-A3D6-11E87E52FAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349D6620-C7B1-47FE-8387-CBA609693E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{02E3CDAF-A272-443C-8687-B38AE8A4CCA2}"/>
   </bookViews>
@@ -340,7 +340,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,12 +354,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFCE9178"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -369,7 +363,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -392,28 +386,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -735,6 +714,7 @@
     <col min="2" max="2" width="82.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -747,10 +727,12 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -761,10 +743,13 @@
       <c r="B2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
         <v>99</v>
       </c>
     </row>
@@ -775,10 +760,13 @@
       <c r="B3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
         <v>99</v>
       </c>
     </row>
@@ -789,10 +777,13 @@
       <c r="B4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
         <v>99</v>
       </c>
     </row>
@@ -803,10 +794,13 @@
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
         <v>99</v>
       </c>
     </row>
@@ -817,10 +811,13 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
         <v>99</v>
       </c>
     </row>
@@ -831,10 +828,13 @@
       <c r="B7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
         <v>99</v>
       </c>
     </row>
@@ -845,10 +845,13 @@
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
         <v>99</v>
       </c>
     </row>
@@ -859,10 +862,13 @@
       <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
         <v>99</v>
       </c>
     </row>
@@ -873,13 +879,15 @@
       <c r="B10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -890,13 +898,15 @@
       <c r="B11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="C11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -907,13 +917,15 @@
       <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="C12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -924,13 +936,15 @@
       <c r="B13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -941,13 +955,15 @@
       <c r="B14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -958,13 +974,15 @@
       <c r="B15" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -975,13 +993,15 @@
       <c r="B16" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="C16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -992,13 +1012,15 @@
       <c r="B17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="C17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1009,13 +1031,15 @@
       <c r="B18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="C18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1026,13 +1050,15 @@
       <c r="B19" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="C19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1043,13 +1069,15 @@
       <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="C20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1060,13 +1088,15 @@
       <c r="B21" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="C21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1077,13 +1107,15 @@
       <c r="B22" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="C22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1094,13 +1126,15 @@
       <c r="B23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="C23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1111,13 +1145,15 @@
       <c r="B24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="C24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1128,13 +1164,15 @@
       <c r="B25" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="C25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1145,13 +1183,15 @@
       <c r="B26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="C26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1162,13 +1202,15 @@
       <c r="B27" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C27" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="C27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1179,13 +1221,15 @@
       <c r="B28" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C28" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="C28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1196,13 +1240,15 @@
       <c r="B29" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C29" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="C29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1213,13 +1259,15 @@
       <c r="B30" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30">
+      <c r="C30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1">
         <v>19</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1230,13 +1278,15 @@
       <c r="B31" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31">
+      <c r="C31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1">
         <v>19</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1247,13 +1297,15 @@
       <c r="B32" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C32" t="s">
-        <v>14</v>
-      </c>
-      <c r="F32">
+      <c r="C32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1">
         <v>19</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1264,13 +1316,15 @@
       <c r="B33" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C33" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33">
+      <c r="C33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1">
         <v>19</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1281,13 +1335,15 @@
       <c r="B34" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C34" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34">
+      <c r="C34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1">
         <v>19</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1298,13 +1354,15 @@
       <c r="B35" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C35" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35">
+      <c r="C35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1">
         <v>19</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1315,13 +1373,15 @@
       <c r="B36" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C36" t="s">
-        <v>14</v>
-      </c>
-      <c r="F36">
+      <c r="C36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1">
         <v>19</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1332,13 +1392,15 @@
       <c r="B37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37">
+      <c r="C37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1">
         <v>19</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1349,13 +1411,15 @@
       <c r="B38" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C38" t="s">
-        <v>14</v>
-      </c>
-      <c r="F38">
+      <c r="C38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1">
         <v>19</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1366,13 +1430,15 @@
       <c r="B39" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C39" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39">
+      <c r="C39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1">
         <v>19</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1383,13 +1449,15 @@
       <c r="B40" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C40" t="s">
-        <v>14</v>
-      </c>
-      <c r="F40">
+      <c r="C40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1">
         <v>19</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1400,13 +1468,15 @@
       <c r="B41" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C41" t="s">
-        <v>14</v>
-      </c>
-      <c r="F41">
+      <c r="C41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1">
         <v>21</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1417,13 +1487,15 @@
       <c r="B42" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C42" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42">
+      <c r="C42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1">
         <v>21</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1434,13 +1506,15 @@
       <c r="B43" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C43" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="C43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="1" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1451,13 +1525,15 @@
       <c r="B44" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C44" t="s">
-        <v>14</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="C44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="1" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1468,13 +1544,15 @@
       <c r="B45" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C45" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="C45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="1" t="s">
         <v>101</v>
       </c>
     </row>
